--- a/audit/aiq-privacy/mcc2026/AIQ_final_shortlist_criteria.xlsx
+++ b/audit/aiq-privacy/mcc2026/AIQ_final_shortlist_criteria.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,95 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NOTE: km and travel times are my estimates from public sources — verify before booking.</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Alternative: connectivity-first weighting (copy these into B8:B13 to switch)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NOTE: bond and PG-quota rules are revised annually. Confirm in the current counselling brochure.</t>
-        </is>
+          <t xml:space="preserve">   Info exposure</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Website staleness</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Connectivity</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Distance from Lucknow</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Fees</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Hindi spoken</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Under connectivity-first: Dhanbad stays #1 (4.00), Bhandara rises to #2 (3.80), Akola drops from #2 to #5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NOTE: km and travel times are my estimates from public sources — verify before booking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NOTE: bond and PG-quota rules are revised annually. Confirm in the current counselling brochure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>NOTE: fees are state tuition estimates per year, excluding hostel/mess/caution deposits.</t>
         </is>

--- a/audit/aiq-privacy/mcc2026/AIQ_final_shortlist_criteria.xlsx
+++ b/audit/aiq-privacy/mcc2026/AIQ_final_shortlist_criteria.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet name="Weights &amp; Method" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Final shortlist" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Verification evidence" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FAILED - avoid" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Segment - 4 new filters" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Verification evidence" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FAILED - avoid" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +41,16 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +75,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007B3F00"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,6 +146,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1860,6 +1879,1507 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:R32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="44" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Segment: no academic calendar + tuition under Rs 40,000 + direct/1-stop flight + not newly founded</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Drawn from BOTH the PASS and FAIL sets, as requested. Privacy verdict is shown so the trade-off is visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Lucknow (LKO) flies direct to 27 airports incl. Kolkata, Delhi, Mumbai, Hyderabad, Chennai, Indore - but NOT Nagpur, Ranchi or Pune.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>2026 R1 close</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>Academic calendar on site</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>Tuition Rs/yr</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>Fee source</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>Under Rs 40k</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Established</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>Age (yrs)</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>Newly founded</t>
+        </is>
+      </c>
+      <c r="L5" s="17" t="inlineStr">
+        <is>
+          <t>Nearest airport</t>
+        </is>
+      </c>
+      <c r="M5" s="17" t="inlineStr">
+        <is>
+          <t>LKO flight</t>
+        </is>
+      </c>
+      <c r="N5" s="17" t="inlineStr">
+        <is>
+          <t>Surface leg</t>
+        </is>
+      </c>
+      <c r="O5" s="17" t="inlineStr">
+        <is>
+          <t>Meets flight+1-2hr</t>
+        </is>
+      </c>
+      <c r="P5" s="17" t="inlineStr">
+        <is>
+          <t>PRIVACY VERDICT</t>
+        </is>
+      </c>
+      <c r="Q5" s="17" t="inlineStr">
+        <is>
+          <t>Passes all 4 filters</t>
+        </is>
+      </c>
+      <c r="R5" s="17" t="inlineStr">
+        <is>
+          <t>What kills it</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>College of Medicine &amp; JNM Hospital</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Kalyani</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>10855</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>WB state estimate - CONFIRM with WBMCC notification</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>Kolkata (CCU)</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>DIRECT from LKO</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>~60 km / ~1.5 hrs</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P6" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q6" s="14" t="inlineStr">
+        <is>
+          <t>PRIVACY: hash-named roster PDF you supplied</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>College of Medicine &amp; Sagore Dutta Hospital</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Kamarhati (Kolkata)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>8626</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>WB state estimate - CONFIRM with WBMCC notification</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>Kolkata (CCU)</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>DIRECT from LKO</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>~15 km / ~40 min</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P7" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q7" s="14" t="inlineStr">
+        <is>
+          <t>PRIVACY: class + full batch lists you found</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Bankura Sammilani Medical College</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Bankura</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>12710</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>WB state estimate - CONFIRM with WBMCC notification</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>1959</v>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>Kolkata (CCU)</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>DIRECT from LKO</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>~200 km / ~4 hrs</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P8" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q8" s="14" t="inlineStr">
+        <is>
+          <t>PRIVACY + surface leg 4 hrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>GMC Ongole (prev. RIMS)</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Ongole</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>17028</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>AP state estimate - CONFIRM with APMC notification</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>Borderline</t>
+        </is>
+      </c>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>Vijayawada (VGA)</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>1-stop via Hyderabad</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>~250 km / ~4.5 hrs</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O9" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P9" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q9" s="14" t="inlineStr">
+        <is>
+          <t>PRIVACY: name+roll+mobile; surface leg 4.5 hrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>GMC Udhampur</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Udhampur</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Jammu &amp; Kashmir</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>14833</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>J&amp;K estimate - at the boundary, not under</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>Jammu (IXJ)</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>1-stop via Delhi</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>~70 km / ~1.5 hrs</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>HIGH RISK</t>
+        </is>
+      </c>
+      <c r="P10" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q10" s="14" t="inlineStr">
+        <is>
+          <t>Fee at boundary; 536-file open dir; J&amp;K dropped by you</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>GMC Latur</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Latur</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>13905</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>85000</v>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>MH state estimate - CONFIRM with state notification</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>Nanded (NDC)</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>1-stop, limited service</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>~130 km / ~2.5 hrs</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O11" s="14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P11" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q11" s="14" t="inlineStr">
+        <is>
+          <t>FEE Rs 85,000; weak connectivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>GMC Akola</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Akola</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>13994</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>85000</v>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>MH state estimate - CONFIRM with state notification</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>Nagpur (NAG)</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>1-stop via Delhi/Mumbai</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>~250 km / ~4.5 hrs</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O12" s="14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P12" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q12" s="14" t="inlineStr">
+        <is>
+          <t>FEE Rs 85,000; worst surface leg on the list</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>GMC Bhandara</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Bhandara</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>18616</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>85000</v>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>MH state estimate - CONFIRM with state notification</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="14" t="inlineStr">
+        <is>
+          <t>Nagpur (NAG)</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>1-stop via Delhi/Mumbai</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>~60 km / ~1.5 hrs</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P13" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q13" s="14" t="inlineStr">
+        <is>
+          <t>FEE Rs 85,000; newly founded</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>GMC Seoni</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Seoni</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>15877</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>MP state estimate - CONFIRM with state notification</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>Nagpur (NAG)</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>1-stop via Delhi/Mumbai</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>~130 km / ~2.5 hrs</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O14" s="14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P14" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q14" s="14" t="inlineStr">
+        <is>
+          <t>FEE Rs 80,000; newly founded</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Shaheed Nirmal Mahto MC, Dhanbad</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Dhanbad</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Jharkhand</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>10303</v>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>YES - 3 docs</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>careers360 reports Rs 8,500 tuition - CONFIRM with college</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>1969</v>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>Ranchi (IXR) / Durgapur (RDP)</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>1-stop via Delhi/Kolkata</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>~140 km / ~3 hrs (rail direct)</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O15" s="14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P15" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q15" s="14" t="inlineStr">
+        <is>
+          <t>HAS academic calendar; surface leg 3 hrs</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>SRTR Ambajogai</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Ambajogai</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>14470</v>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>85000</v>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>MH state estimate</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>1975</v>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>Nanded (NDC)</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>1-stop, limited service</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>~90 km / ~2 hrs</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O16" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P16" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q16" s="14" t="inlineStr">
+        <is>
+          <t>HAS calendar; FEE Rs 85,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>GMC Chandrapur</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Chandrapur</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>15048</v>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>85000</v>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>MH state estimate</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>2015</v>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Borderline</t>
+        </is>
+      </c>
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>Nagpur (NAG)</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>1-stop via Delhi/Mumbai</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>~150 km / ~3 hrs</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O17" s="14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P17" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q17" s="14" t="inlineStr">
+        <is>
+          <t>HAS calendar; FEE Rs 85,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>GMC Ratnagiri</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>16082</v>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>85000</v>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>MH state estimate</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>Kolhapur (KLH)</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>1-stop via Mumbai</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>~130 km / ~3 hrs</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" s="14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P18" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q18" s="14" t="inlineStr">
+        <is>
+          <t>HAS calendar; FEE Rs 85,000; newly founded</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>JLN Medical College, Bhagalpur</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Bhagalpur</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>10357</v>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>Bihar state estimate - CONFIRM</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>1971</v>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" s="14" t="inlineStr">
+        <is>
+          <t>Patna (PAT)</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>1-stop via Delhi</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>~220 km / ~4.5 hrs</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O19" s="14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P19" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q19" s="14" t="inlineStr">
+        <is>
+          <t>HAS calendar; surface 4.5 hrs; you excluded as too near</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Medinirai MC, Palamu</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Daltonganj</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Jharkhand</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>not allotted R1</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Jharkhand estimate</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>Ranchi (IXR)</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>1-stop via Delhi</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>~170 km / ~3.5 hrs</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O20" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="P20" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q20" s="14" t="inlineStr">
+        <is>
+          <t>PRIVACY: current-intake student list; HAS calendar; newly founded</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>GMC Baramulla</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Baramulla</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Jammu &amp; Kashmir</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>17201</v>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>J&amp;K estimate - at boundary</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>Srinagar (SXR)</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>1-stop via Delhi</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>~55 km / ~1.5 hrs</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O21" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P21" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q21" s="14" t="inlineStr">
+        <is>
+          <t>HAS calendar; newly founded; J&amp;K dropped by you</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>RESULT: no college satisfies all four filters at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>The four criteria are best met by the Kolkata-belt West Bengal colleges - cheapest tuition, the only DIRECT Lucknow flight,</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>a 40-90 minute surface hop, no academic calendar, and decades old. All of them publish student data (confirmed FAILs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>The privacy-clean colleges that clear the calendar filter - Latur, Akola, Bhandara, Seoni - all fail the Rs 40k fee gate at Rs 80-85k.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>CLOSEST TO YOUR FOUR FILTERS, privacy intact: GMC Latur and GMC Akola (no calendar, established 2002, PASS) - blocked only by fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>CLOSEST on flight rule, privacy intact: GMC Bhandara (Nagpur ~60 km) - blocked by fee and by being founded 2019.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>All tuition figures are state-level estimates unless the Fee source column says otherwise. Confirm against the state fee notification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Airport distances and surface times are my estimates. Verify before relying on them.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2072,7 +3592,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
